--- a/Project/DiceWarrior/LubanTool/Datas/__tables__.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/__tables__.xlsx
@@ -1032,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="6.25" customWidth="1" style="3" min="1" max="1"/>
@@ -1364,6 +1364,50 @@
         </is>
       </c>
     </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TBEventCardCategory</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EventCard</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EventCard.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DiceBattleCategory</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DiceBattle</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DiceBattle.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
